--- a/Team-Data/2008-09/3-24-2008-09.xlsx
+++ b/Team-Data/2008-09/3-24-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -754,13 +821,13 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ2" t="n">
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -775,7 +842,7 @@
         <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -784,7 +851,7 @@
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>21</v>
@@ -799,7 +866,7 @@
         <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -811,7 +878,7 @@
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>0.746</v>
+        <v>0.75</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
@@ -861,28 +928,28 @@
         <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.486</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
         <v>16.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.396</v>
+        <v>0.394</v>
       </c>
       <c r="O3" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P3" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>10.5</v>
@@ -891,10 +958,10 @@
         <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.7</v>
@@ -909,19 +976,19 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA3" t="n">
         <v>22.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
@@ -954,13 +1021,13 @@
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -981,10 +1048,10 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -993,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1145,7 +1212,7 @@
         <v>26</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
         <v>26</v>
@@ -1172,13 +1239,13 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -1225,10 +1292,10 @@
         <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -1237,19 +1304,19 @@
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O5" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R5" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S5" t="n">
         <v>30.6</v>
@@ -1258,10 +1325,10 @@
         <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
         <v>7.4</v>
@@ -1276,16 +1343,16 @@
         <v>21.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1315,13 +1382,13 @@
         <v>23</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1339,10 +1406,10 @@
         <v>15</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
         <v>5</v>
@@ -1354,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
         <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -1389,43 +1456,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" t="n">
         <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.826</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
         <v>20.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.388</v>
+        <v>0.386</v>
       </c>
       <c r="O6" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0.752</v>
@@ -1440,10 +1507,10 @@
         <v>41.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.5</v>
@@ -1455,19 +1522,19 @@
         <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.4</v>
+        <v>100.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1491,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM6" t="n">
         <v>5</v>
@@ -1500,7 +1567,7 @@
         <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1527,7 +1594,7 @@
         <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>4</v>
@@ -1536,7 +1603,7 @@
         <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>14</v>
@@ -1694,10 +1761,10 @@
         <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
         <v>10</v>
@@ -1721,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -1831,13 +1898,13 @@
         <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
         <v>8</v>
@@ -1846,7 +1913,7 @@
         <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
         <v>23</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1888,7 +1955,7 @@
         <v>26</v>
       </c>
       <c r="AW8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
         <v>3</v>
@@ -1900,7 +1967,7 @@
         <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>6</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="n">
         <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J9" t="n">
-        <v>80.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="K9" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
@@ -1965,13 +2032,13 @@
         <v>12.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="P9" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0.753</v>
@@ -1983,10 +2050,10 @@
         <v>29.7</v>
       </c>
       <c r="T9" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U9" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V9" t="n">
         <v>11.8</v>
@@ -2010,10 +2077,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2028,7 +2095,7 @@
         <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
         <v>18</v>
@@ -2076,7 +2143,7 @@
         <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -2117,43 +2184,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>0.352</v>
+        <v>0.357</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L10" t="n">
         <v>6.6</v>
       </c>
       <c r="M10" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="O10" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="P10" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="Q10" t="n">
         <v>0.786</v>
@@ -2162,22 +2229,22 @@
         <v>11.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T10" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X10" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y10" t="n">
         <v>5</v>
@@ -2189,25 +2256,25 @@
         <v>23.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.5</v>
+        <v>108.6</v>
       </c>
       <c r="AC10" t="n">
         <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>16</v>
@@ -2234,13 +2301,13 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -2249,7 +2316,7 @@
         <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2258,10 +2325,10 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA10" t="n">
         <v>3</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
         <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.644</v>
+        <v>0.653</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J11" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L11" t="n">
         <v>7.6</v>
@@ -2329,31 +2396,31 @@
         <v>20.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O11" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P11" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0.806</v>
       </c>
       <c r="R11" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S11" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U11" t="n">
         <v>20.4</v>
       </c>
       <c r="V11" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W11" t="n">
         <v>6.8</v>
@@ -2368,13 +2435,13 @@
         <v>18.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
@@ -2383,10 +2450,10 @@
         <v>5</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH11" t="n">
         <v>18</v>
@@ -2410,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2422,16 +2489,16 @@
         <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2440,7 +2507,7 @@
         <v>25</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2449,10 +2516,10 @@
         <v>15</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2571,7 +2638,7 @@
         <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2583,7 +2650,7 @@
         <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
         <v>3</v>
@@ -2613,7 +2680,7 @@
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI13" t="n">
         <v>27</v>
@@ -2786,7 +2853,7 @@
         <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>24</v>
@@ -2795,7 +2862,7 @@
         <v>11</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
         <v>23</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -2860,13 +2927,13 @@
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="J14" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L14" t="n">
         <v>6.9</v>
@@ -2875,7 +2942,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O14" t="n">
         <v>19.8</v>
@@ -2884,28 +2951,28 @@
         <v>25.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
         <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
         <v>23.5</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
         <v>4.7</v>
@@ -2917,13 +2984,13 @@
         <v>22.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.4</v>
+        <v>108.2</v>
       </c>
       <c r="AC14" t="n">
         <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2953,10 +3020,10 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2980,16 +3047,16 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY14" t="n">
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3208,7 @@
         <v>15</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
@@ -3359,7 +3426,7 @@
         <v>24</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17" t="n">
         <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>0.443</v>
+        <v>0.437</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3421,67 +3488,67 @@
         <v>16.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P17" t="n">
         <v>25.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.5</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y17" t="n">
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
         <v>19</v>
@@ -3505,7 +3572,7 @@
         <v>6</v>
       </c>
       <c r="AP17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3514,25 +3581,25 @@
         <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
         <v>9</v>
       </c>
       <c r="AV17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW17" t="n">
         <v>13</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>12</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3541,7 +3608,7 @@
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC17" t="n">
         <v>17</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3718,19 @@
         <v>-4.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
         <v>16</v>
@@ -3675,7 +3742,7 @@
         <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM18" t="n">
         <v>15</v>
@@ -3684,13 +3751,13 @@
         <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3705,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3723,7 +3790,7 @@
         <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3906,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
@@ -3857,19 +3924,19 @@
         <v>22</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
@@ -3893,7 +3960,7 @@
         <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY19" t="n">
         <v>15</v>
@@ -3905,7 +3972,7 @@
         <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4368,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" t="n">
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>0.282</v>
+        <v>0.286</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J22" t="n">
         <v>81.90000000000001</v>
@@ -4328,31 +4395,31 @@
         <v>4.1</v>
       </c>
       <c r="M22" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.349</v>
+        <v>0.353</v>
       </c>
       <c r="O22" t="n">
         <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R22" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S22" t="n">
         <v>30.5</v>
       </c>
       <c r="T22" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V22" t="n">
         <v>16.6</v>
@@ -4364,7 +4431,7 @@
         <v>4.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z22" t="n">
         <v>20.6</v>
@@ -4373,13 +4440,13 @@
         <v>20.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>25</v>
@@ -4391,7 +4458,7 @@
         <v>25</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>15</v>
@@ -4400,7 +4467,7 @@
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,7 +4476,7 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO22" t="n">
         <v>7</v>
@@ -4418,7 +4485,7 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR22" t="n">
         <v>4</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,10 +4512,10 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB22" t="n">
         <v>23</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4621,7 +4688,7 @@
         <v>19</v>
       </c>
       <c r="AX23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY23" t="n">
         <v>2</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4758,7 +4825,7 @@
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
         <v>16</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -5029,55 +5096,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
         <v>44</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.629</v>
+        <v>0.62</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
         <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T26" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U26" t="n">
         <v>20.2</v>
@@ -5098,37 +5165,37 @@
         <v>20.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.2</v>
+        <v>98.8</v>
       </c>
       <c r="AC26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD26" t="n">
         <v>4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>9</v>
@@ -5137,13 +5204,13 @@
         <v>11</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>15</v>
@@ -5158,7 +5225,7 @@
         <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
@@ -5173,16 +5240,16 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI27" t="n">
         <v>23</v>
@@ -5310,7 +5377,7 @@
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
         <v>11</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n">
         <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.657</v>
+        <v>0.652</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J28" t="n">
         <v>79.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L28" t="n">
         <v>7.7</v>
@@ -5426,25 +5493,25 @@
         <v>0.392</v>
       </c>
       <c r="O28" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P28" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T28" t="n">
         <v>41.1</v>
       </c>
       <c r="U28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V28" t="n">
         <v>12</v>
@@ -5465,13 +5532,13 @@
         <v>18.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5480,13 +5547,13 @@
         <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="n">
         <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ28" t="n">
         <v>20</v>
@@ -5516,7 +5583,7 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT28" t="n">
         <v>19</v>
@@ -5546,7 +5613,7 @@
         <v>24</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5735,7 @@
         <v>20</v>
       </c>
       <c r="AI29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
         <v>17</v>
@@ -5686,7 +5753,7 @@
         <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP29" t="n">
         <v>26</v>
@@ -5710,10 +5777,10 @@
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F30" t="n">
         <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,7 +5842,7 @@
         <v>38.5</v>
       </c>
       <c r="J30" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.477</v>
@@ -5787,22 +5854,22 @@
         <v>13.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O30" t="n">
         <v>21.5</v>
       </c>
       <c r="P30" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="Q30" t="n">
         <v>0.773</v>
       </c>
       <c r="R30" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S30" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T30" t="n">
         <v>41.2</v>
@@ -5811,37 +5878,37 @@
         <v>24.8</v>
       </c>
       <c r="V30" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W30" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y30" t="n">
         <v>5</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>103.1</v>
+        <v>103.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF30" t="n">
         <v>8</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>7</v>
       </c>
       <c r="AG30" t="n">
         <v>9</v>
@@ -5877,10 +5944,10 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
         <v>17</v>
@@ -5889,28 +5956,28 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB30" t="n">
         <v>7</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-8</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6068,7 +6135,7 @@
         <v>22</v>
       </c>
       <c r="AU31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
@@ -6080,7 +6147,7 @@
         <v>26</v>
       </c>
       <c r="AY31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-24-2008-09</t>
+          <t>2009-03-24</t>
         </is>
       </c>
     </row>
